--- a/research/DOW.NZ/Reports/DOW.NZ_DCF_Model.xlsx
+++ b/research/DOW.NZ/Reports/DOW.NZ_DCF_Model.xlsx
@@ -2633,9 +2633,10 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B8" s="6">
         <v>176.7</v>
